--- a/src/excel-data/toukai.xlsx
+++ b/src/excel-data/toukai.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Applications/Cao Yuxuan/テストweb/findmyrailpass.net/src/excel-data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E94CB66D-71FB-234F-BB09-876C8BB98D75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{764107DC-9F50-674C-A3FC-FDABC9EE2DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27860" yWindow="3440" windowWidth="22840" windowHeight="18960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2720" yWindow="3260" windowWidth="22840" windowHeight="18960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="toukai周游券" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="380">
   <si>
     <t>sortOrder</t>
   </si>
@@ -1566,12 +1566,65 @@
     <t>三重；阿下喜；</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>https://touristpass.jp/zh-cn/</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>特急电车; 急行电车; 普通电车;巴士</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Mt-Fuji-Shizuoka-Area</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>/images/coverage/Mt-Fuji-Shizuoka-Area.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>富士山静冈区域3日周游券</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>全年可用</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>持有旅游签证的外国护照游客</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>富士山</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="黒体-簡 ミディアム"/>
+        <charset val="134"/>
+      </rPr>
+      <t>静岡エリア</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1631,6 +1684,13 @@
       <name val="黒体-簡 ミディアム"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="MS Mincho"/>
+      <family val="1"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1659,7 +1719,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1675,6 +1735,8 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -2131,6 +2193,9 @@
       <c r="AE1" s="2"/>
     </row>
     <row r="2" spans="1:31" s="3" customFormat="1">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
       <c r="B2" s="4" t="s">
         <v>29</v>
       </c>
@@ -2190,6 +2255,9 @@
       </c>
     </row>
     <row r="3" spans="1:31" s="3" customFormat="1">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
       <c r="B3" s="4" t="s">
         <v>32</v>
       </c>
@@ -2246,6 +2314,9 @@
       </c>
     </row>
     <row r="4" spans="1:31" s="3" customFormat="1">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
       <c r="B4" s="4" t="s">
         <v>35</v>
       </c>
@@ -2305,6 +2376,9 @@
       </c>
     </row>
     <row r="5" spans="1:31" s="3" customFormat="1" ht="48">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
       <c r="B5" s="4" t="s">
         <v>38</v>
       </c>
@@ -2354,7 +2428,7 @@
         <v>185</v>
       </c>
       <c r="Z5" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB5" s="7" t="s">
         <v>201</v>
@@ -2364,6 +2438,9 @@
       </c>
     </row>
     <row r="6" spans="1:31" s="3" customFormat="1" ht="48">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
       <c r="B6" s="4" t="s">
         <v>41</v>
       </c>
@@ -2423,6 +2500,9 @@
       </c>
     </row>
     <row r="7" spans="1:31" s="3" customFormat="1" ht="48">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
       <c r="B7" s="4" t="s">
         <v>44</v>
       </c>
@@ -2482,6 +2562,9 @@
       </c>
     </row>
     <row r="8" spans="1:31" s="3" customFormat="1" ht="32">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
       <c r="B8" s="4" t="s">
         <v>47</v>
       </c>
@@ -2528,7 +2611,7 @@
         <v>185</v>
       </c>
       <c r="Z8" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AA8" s="3" t="b">
         <v>1</v>
@@ -2541,6 +2624,9 @@
       </c>
     </row>
     <row r="9" spans="1:31" s="3" customFormat="1" ht="32">
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
       <c r="B9" s="4" t="s">
         <v>50</v>
       </c>
@@ -2600,6 +2686,9 @@
       </c>
     </row>
     <row r="10" spans="1:31" s="3" customFormat="1" ht="16">
+      <c r="A10" s="3">
+        <v>9</v>
+      </c>
       <c r="B10" s="4" t="s">
         <v>53</v>
       </c>
@@ -2649,7 +2738,7 @@
         <v>185</v>
       </c>
       <c r="Z10" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA10" s="3" t="b">
         <v>1</v>
@@ -2662,6 +2751,9 @@
       </c>
     </row>
     <row r="11" spans="1:31" s="3" customFormat="1">
+      <c r="A11" s="3">
+        <v>10</v>
+      </c>
       <c r="B11" s="4" t="s">
         <v>56</v>
       </c>
@@ -2718,6 +2810,9 @@
       </c>
     </row>
     <row r="12" spans="1:31" s="3" customFormat="1">
+      <c r="A12" s="3">
+        <v>11</v>
+      </c>
       <c r="B12" s="4" t="s">
         <v>58</v>
       </c>
@@ -2777,6 +2872,9 @@
       </c>
     </row>
     <row r="13" spans="1:31" s="3" customFormat="1" ht="16">
+      <c r="A13" s="3">
+        <v>12</v>
+      </c>
       <c r="B13" s="4" t="s">
         <v>61</v>
       </c>
@@ -2823,7 +2921,7 @@
         <v>185</v>
       </c>
       <c r="Z13" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB13" s="7" t="s">
         <v>288</v>
@@ -2833,6 +2931,9 @@
       </c>
     </row>
     <row r="14" spans="1:31" s="3" customFormat="1" ht="16">
+      <c r="A14" s="3">
+        <v>13</v>
+      </c>
       <c r="B14" s="4" t="s">
         <v>64</v>
       </c>
@@ -2879,7 +2980,7 @@
         <v>185</v>
       </c>
       <c r="Z14" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB14" s="7" t="s">
         <v>288</v>
@@ -2889,6 +2990,9 @@
       </c>
     </row>
     <row r="15" spans="1:31" s="3" customFormat="1">
+      <c r="A15" s="3">
+        <v>14</v>
+      </c>
       <c r="B15" s="4" t="s">
         <v>67</v>
       </c>
@@ -2942,6 +3046,9 @@
       </c>
     </row>
     <row r="16" spans="1:31" s="3" customFormat="1">
+      <c r="A16" s="3">
+        <v>15</v>
+      </c>
       <c r="B16" s="4" t="s">
         <v>70</v>
       </c>
@@ -2994,7 +3101,10 @@
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="2:30" s="3" customFormat="1">
+    <row r="17" spans="1:30" s="3" customFormat="1">
+      <c r="A17" s="3">
+        <v>16</v>
+      </c>
       <c r="B17" s="4" t="s">
         <v>73</v>
       </c>
@@ -3050,7 +3160,10 @@
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="2:30" s="3" customFormat="1">
+    <row r="18" spans="1:30" s="3" customFormat="1">
+      <c r="A18" s="3">
+        <v>17</v>
+      </c>
       <c r="B18" s="4" t="s">
         <v>76</v>
       </c>
@@ -3106,7 +3219,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" spans="2:30" s="3" customFormat="1">
+    <row r="19" spans="1:30" s="3" customFormat="1">
+      <c r="A19" s="3">
+        <v>18</v>
+      </c>
       <c r="B19" s="4" t="s">
         <v>79</v>
       </c>
@@ -3162,7 +3278,10 @@
         <v>80</v>
       </c>
     </row>
-    <row r="20" spans="2:30" s="3" customFormat="1">
+    <row r="20" spans="1:30" s="3" customFormat="1">
+      <c r="A20" s="3">
+        <v>19</v>
+      </c>
       <c r="B20" s="4" t="s">
         <v>213</v>
       </c>
@@ -3215,7 +3334,10 @@
         <v>82</v>
       </c>
     </row>
-    <row r="21" spans="2:30" s="3" customFormat="1">
+    <row r="21" spans="1:30" s="3" customFormat="1">
+      <c r="A21" s="3">
+        <v>20</v>
+      </c>
       <c r="B21" s="4" t="s">
         <v>214</v>
       </c>
@@ -3268,7 +3390,10 @@
         <v>82</v>
       </c>
     </row>
-    <row r="22" spans="2:30" s="3" customFormat="1">
+    <row r="22" spans="1:30" s="3" customFormat="1">
+      <c r="A22" s="3">
+        <v>21</v>
+      </c>
       <c r="B22" s="4" t="s">
         <v>83</v>
       </c>
@@ -3327,7 +3452,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="2:30" s="3" customFormat="1">
+    <row r="23" spans="1:30" s="3" customFormat="1">
+      <c r="A23" s="3">
+        <v>22</v>
+      </c>
       <c r="B23" s="4" t="s">
         <v>86</v>
       </c>
@@ -3383,7 +3511,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="24" spans="2:30" s="3" customFormat="1">
+    <row r="24" spans="1:30" s="3" customFormat="1">
+      <c r="A24" s="3">
+        <v>23</v>
+      </c>
       <c r="B24" s="4" t="s">
         <v>89</v>
       </c>
@@ -3442,7 +3573,10 @@
         <v>90</v>
       </c>
     </row>
-    <row r="25" spans="2:30" s="3" customFormat="1">
+    <row r="25" spans="1:30" s="3" customFormat="1">
+      <c r="A25" s="3">
+        <v>24</v>
+      </c>
       <c r="B25" s="4" t="s">
         <v>92</v>
       </c>
@@ -3501,7 +3635,10 @@
         <v>93</v>
       </c>
     </row>
-    <row r="26" spans="2:30" s="3" customFormat="1">
+    <row r="26" spans="1:30" s="3" customFormat="1">
+      <c r="A26" s="3">
+        <v>25</v>
+      </c>
       <c r="B26" s="4" t="s">
         <v>95</v>
       </c>
@@ -3560,7 +3697,10 @@
         <v>96</v>
       </c>
     </row>
-    <row r="27" spans="2:30" s="3" customFormat="1">
+    <row r="27" spans="1:30" s="3" customFormat="1">
+      <c r="A27" s="3">
+        <v>26</v>
+      </c>
       <c r="B27" s="4" t="s">
         <v>98</v>
       </c>
@@ -3607,13 +3747,16 @@
         <v>185</v>
       </c>
       <c r="Z27" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD27" s="4" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="28" spans="2:30" s="3" customFormat="1">
+    <row r="28" spans="1:30" s="3" customFormat="1">
+      <c r="A28" s="3">
+        <v>27</v>
+      </c>
       <c r="B28" s="4" t="s">
         <v>101</v>
       </c>
@@ -3660,13 +3803,16 @@
         <v>185</v>
       </c>
       <c r="Z28" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD28" s="4" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="29" spans="2:30" s="3" customFormat="1">
+    <row r="29" spans="1:30" s="3" customFormat="1">
+      <c r="A29" s="3">
+        <v>28</v>
+      </c>
       <c r="B29" s="4" t="s">
         <v>228</v>
       </c>
@@ -3719,7 +3865,10 @@
         <v>326</v>
       </c>
     </row>
-    <row r="30" spans="2:30" s="3" customFormat="1">
+    <row r="30" spans="1:30" s="3" customFormat="1">
+      <c r="A30" s="3">
+        <v>29</v>
+      </c>
       <c r="B30" s="4" t="s">
         <v>229</v>
       </c>
@@ -3772,7 +3921,10 @@
         <v>328</v>
       </c>
     </row>
-    <row r="31" spans="2:30" s="3" customFormat="1">
+    <row r="31" spans="1:30" s="3" customFormat="1">
+      <c r="A31" s="3">
+        <v>30</v>
+      </c>
       <c r="B31" s="4" t="s">
         <v>104</v>
       </c>
@@ -3825,7 +3977,10 @@
         <v>105</v>
       </c>
     </row>
-    <row r="32" spans="2:30" s="3" customFormat="1">
+    <row r="32" spans="1:30" s="3" customFormat="1">
+      <c r="A32" s="3">
+        <v>31</v>
+      </c>
       <c r="B32" s="4" t="s">
         <v>104</v>
       </c>
@@ -3878,7 +4033,10 @@
         <v>105</v>
       </c>
     </row>
-    <row r="33" spans="2:30" s="3" customFormat="1">
+    <row r="33" spans="1:30" s="3" customFormat="1">
+      <c r="A33" s="3">
+        <v>32</v>
+      </c>
       <c r="B33" s="4" t="s">
         <v>104</v>
       </c>
@@ -3931,7 +4089,10 @@
         <v>105</v>
       </c>
     </row>
-    <row r="34" spans="2:30" s="3" customFormat="1">
+    <row r="34" spans="1:30" s="3" customFormat="1">
+      <c r="A34" s="3">
+        <v>33</v>
+      </c>
       <c r="B34" s="4" t="s">
         <v>106</v>
       </c>
@@ -3975,13 +4136,16 @@
         <v>185</v>
       </c>
       <c r="Z34" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD34" s="4" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="35" spans="2:30" s="3" customFormat="1">
+    <row r="35" spans="1:30" s="3" customFormat="1">
+      <c r="A35" s="3">
+        <v>34</v>
+      </c>
       <c r="B35" s="4" t="s">
         <v>106</v>
       </c>
@@ -4025,13 +4189,16 @@
         <v>185</v>
       </c>
       <c r="Z35" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD35" s="4" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="36" spans="2:30" s="3" customFormat="1">
+    <row r="36" spans="1:30" s="3" customFormat="1">
+      <c r="A36" s="3">
+        <v>35</v>
+      </c>
       <c r="B36" s="4" t="s">
         <v>106</v>
       </c>
@@ -4075,13 +4242,16 @@
         <v>185</v>
       </c>
       <c r="Z36" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD36" s="4" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="37" spans="2:30" s="3" customFormat="1">
+    <row r="37" spans="1:30" s="3" customFormat="1">
+      <c r="A37" s="3">
+        <v>36</v>
+      </c>
       <c r="B37" s="4" t="s">
         <v>108</v>
       </c>
@@ -4131,7 +4301,10 @@
         <v>109</v>
       </c>
     </row>
-    <row r="38" spans="2:30" s="3" customFormat="1">
+    <row r="38" spans="1:30" s="3" customFormat="1">
+      <c r="A38" s="3">
+        <v>37</v>
+      </c>
       <c r="B38" s="4" t="s">
         <v>111</v>
       </c>
@@ -4181,7 +4354,10 @@
         <v>112</v>
       </c>
     </row>
-    <row r="39" spans="2:30" s="3" customFormat="1">
+    <row r="39" spans="1:30" s="3" customFormat="1">
+      <c r="A39" s="3">
+        <v>38</v>
+      </c>
       <c r="B39" s="4" t="s">
         <v>114</v>
       </c>
@@ -4231,7 +4407,10 @@
         <v>115</v>
       </c>
     </row>
-    <row r="40" spans="2:30" s="3" customFormat="1" ht="16">
+    <row r="40" spans="1:30" s="3" customFormat="1" ht="16">
+      <c r="A40" s="3">
+        <v>39</v>
+      </c>
       <c r="B40" s="4" t="s">
         <v>117</v>
       </c>
@@ -4284,7 +4463,10 @@
         <v>118</v>
       </c>
     </row>
-    <row r="41" spans="2:30" s="3" customFormat="1">
+    <row r="41" spans="1:30" s="3" customFormat="1">
+      <c r="A41" s="3">
+        <v>40</v>
+      </c>
       <c r="B41" s="4" t="s">
         <v>120</v>
       </c>
@@ -4334,7 +4516,10 @@
         <v>121</v>
       </c>
     </row>
-    <row r="42" spans="2:30" s="3" customFormat="1">
+    <row r="42" spans="1:30" s="3" customFormat="1">
+      <c r="A42" s="3">
+        <v>41</v>
+      </c>
       <c r="B42" s="4" t="s">
         <v>123</v>
       </c>
@@ -4384,7 +4569,10 @@
         <v>124</v>
       </c>
     </row>
-    <row r="43" spans="2:30" s="3" customFormat="1">
+    <row r="43" spans="1:30" s="3" customFormat="1">
+      <c r="A43" s="3">
+        <v>42</v>
+      </c>
       <c r="B43" s="4" t="s">
         <v>126</v>
       </c>
@@ -4425,13 +4613,16 @@
         <v>254</v>
       </c>
       <c r="Z43" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD43" s="4" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="44" spans="2:30" s="3" customFormat="1">
+    <row r="44" spans="1:30" s="3" customFormat="1">
+      <c r="A44" s="3">
+        <v>43</v>
+      </c>
       <c r="B44" s="4" t="s">
         <v>255</v>
       </c>
@@ -4472,13 +4663,16 @@
         <v>254</v>
       </c>
       <c r="Z44" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD44" s="4" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="45" spans="2:30" s="3" customFormat="1">
+    <row r="45" spans="1:30" s="3" customFormat="1">
+      <c r="A45" s="3">
+        <v>44</v>
+      </c>
       <c r="B45" s="4" t="s">
         <v>129</v>
       </c>
@@ -4519,13 +4713,16 @@
         <v>254</v>
       </c>
       <c r="Z45" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD45" s="4" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="46" spans="2:30" s="3" customFormat="1">
+    <row r="46" spans="1:30" s="3" customFormat="1">
+      <c r="A46" s="3">
+        <v>45</v>
+      </c>
       <c r="B46" s="4" t="s">
         <v>131</v>
       </c>
@@ -4575,7 +4772,10 @@
         <v>132</v>
       </c>
     </row>
-    <row r="47" spans="2:30" s="3" customFormat="1">
+    <row r="47" spans="1:30" s="3" customFormat="1">
+      <c r="A47" s="3">
+        <v>46</v>
+      </c>
       <c r="B47" s="4" t="s">
         <v>134</v>
       </c>
@@ -4622,7 +4822,7 @@
         <v>185</v>
       </c>
       <c r="Z47" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB47" s="3" t="s">
         <v>288</v>
@@ -4631,7 +4831,10 @@
         <v>135</v>
       </c>
     </row>
-    <row r="48" spans="2:30" s="3" customFormat="1">
+    <row r="48" spans="1:30" s="3" customFormat="1">
+      <c r="A48" s="3">
+        <v>47</v>
+      </c>
       <c r="B48" s="4" t="s">
         <v>137</v>
       </c>
@@ -4674,7 +4877,7 @@
         <v>185</v>
       </c>
       <c r="Z48" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB48" s="3" t="s">
         <v>288</v>
@@ -4683,7 +4886,10 @@
         <v>138</v>
       </c>
     </row>
-    <row r="49" spans="2:30" s="3" customFormat="1" ht="32">
+    <row r="49" spans="1:30" s="3" customFormat="1" ht="32">
+      <c r="A49" s="3">
+        <v>48</v>
+      </c>
       <c r="B49" s="4" t="s">
         <v>140</v>
       </c>
@@ -4745,7 +4951,10 @@
         <v>141</v>
       </c>
     </row>
-    <row r="50" spans="2:30" s="3" customFormat="1">
+    <row r="50" spans="1:30" s="3" customFormat="1">
+      <c r="A50" s="3">
+        <v>49</v>
+      </c>
       <c r="B50" s="4" t="s">
         <v>143</v>
       </c>
@@ -4788,13 +4997,16 @@
         <v>185</v>
       </c>
       <c r="Z50" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AD50" s="4" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="51" spans="2:30" s="3" customFormat="1" ht="16">
+    <row r="51" spans="1:30" s="3" customFormat="1" ht="16">
+      <c r="A51" s="3">
+        <v>50</v>
+      </c>
       <c r="B51" s="4" t="s">
         <v>146</v>
       </c>
@@ -4840,7 +5052,7 @@
         <v>185</v>
       </c>
       <c r="Z51" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AA51" s="3" t="b">
         <v>1</v>
@@ -4852,7 +5064,10 @@
         <v>147</v>
       </c>
     </row>
-    <row r="52" spans="2:30" s="3" customFormat="1">
+    <row r="52" spans="1:30" s="3" customFormat="1">
+      <c r="A52" s="3">
+        <v>51</v>
+      </c>
       <c r="B52" s="4" t="s">
         <v>149</v>
       </c>
@@ -4899,7 +5114,10 @@
         <v>174</v>
       </c>
     </row>
-    <row r="53" spans="2:30" s="3" customFormat="1">
+    <row r="53" spans="1:30" s="3" customFormat="1">
+      <c r="A53" s="3">
+        <v>52</v>
+      </c>
       <c r="B53" s="4" t="s">
         <v>151</v>
       </c>
@@ -4951,7 +5169,10 @@
         <v>152</v>
       </c>
     </row>
-    <row r="54" spans="2:30" s="3" customFormat="1">
+    <row r="54" spans="1:30" s="3" customFormat="1">
+      <c r="A54" s="3">
+        <v>53</v>
+      </c>
       <c r="B54" s="4" t="s">
         <v>154</v>
       </c>
@@ -5006,7 +5227,10 @@
         <v>90</v>
       </c>
     </row>
-    <row r="55" spans="2:30" s="3" customFormat="1">
+    <row r="55" spans="1:30" s="3" customFormat="1">
+      <c r="A55" s="3">
+        <v>54</v>
+      </c>
       <c r="B55" s="4" t="s">
         <v>156</v>
       </c>
@@ -5058,7 +5282,10 @@
         <v>157</v>
       </c>
     </row>
-    <row r="56" spans="2:30" s="3" customFormat="1">
+    <row r="56" spans="1:30" s="3" customFormat="1">
+      <c r="A56" s="3">
+        <v>55</v>
+      </c>
       <c r="B56" s="4" t="s">
         <v>159</v>
       </c>
@@ -5110,7 +5337,10 @@
         <v>74</v>
       </c>
     </row>
-    <row r="57" spans="2:30" s="3" customFormat="1">
+    <row r="57" spans="1:30" s="3" customFormat="1">
+      <c r="A57" s="3">
+        <v>56</v>
+      </c>
       <c r="B57" s="4" t="s">
         <v>161</v>
       </c>
@@ -5159,11 +5389,14 @@
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="2:30" s="3" customFormat="1">
+    <row r="58" spans="1:30" s="3" customFormat="1">
+      <c r="A58" s="3">
+        <v>57</v>
+      </c>
       <c r="B58" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="C58" s="4" t="s">
+      <c r="C58" s="11" t="s">
         <v>367</v>
       </c>
       <c r="E58" s="5">
@@ -5206,7 +5439,10 @@
         <v>175</v>
       </c>
     </row>
-    <row r="59" spans="2:30" s="3" customFormat="1">
+    <row r="59" spans="1:30" s="3" customFormat="1">
+      <c r="A59" s="3">
+        <v>58</v>
+      </c>
       <c r="B59" s="4" t="s">
         <v>166</v>
       </c>
@@ -5251,6 +5487,64 @@
       </c>
       <c r="AD59" s="4" t="s">
         <v>176</v>
+      </c>
+    </row>
+    <row r="60" spans="1:30" s="4" customFormat="1">
+      <c r="A60" s="3">
+        <v>59</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="C60" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="E60" s="5">
+        <v>6500</v>
+      </c>
+      <c r="F60" s="5"/>
+      <c r="G60" s="5">
+        <v>3250</v>
+      </c>
+      <c r="N60" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="O60" s="3">
+        <v>3</v>
+      </c>
+      <c r="P60" s="3"/>
+      <c r="Q60" s="3"/>
+      <c r="R60" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="S60" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="T60" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="U60" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="V60" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="W60" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="X60" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="Y60" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="Z60" s="3">
+        <v>5</v>
+      </c>
+      <c r="AA60" s="3"/>
+      <c r="AB60" s="3"/>
+      <c r="AD60" s="11" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="101" spans="11:13">
@@ -5629,6 +5923,8 @@
     <hyperlink ref="W57" r:id="rId91" xr:uid="{0222D865-AD2E-CF4F-B1C5-71384DF575BD}"/>
     <hyperlink ref="W58" r:id="rId92" xr:uid="{E2667699-73B5-9E4D-9F1E-627D35225D08}"/>
     <hyperlink ref="W59" r:id="rId93" xr:uid="{96201CB6-5F6E-4C47-B184-B19F18B5E019}"/>
+    <hyperlink ref="W60" r:id="rId94" xr:uid="{65F2CF6F-EA2A-B441-A486-87F9654E36AD}"/>
+    <hyperlink ref="X60" r:id="rId95" xr:uid="{3A2A8DCB-6911-2140-813D-8EFB53CF32DA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
